--- a/data/hydroExample/Power_HydroNetwork.xlsx
+++ b/data/hydroExample/Power_HydroNetwork.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E8CC23-F63B-4FE4-8943-95E969852F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E8CCB-0FC9-477C-9312-DEEEC962A5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario_2014" sheetId="1" r:id="rId1"/>
+    <sheet name="Scenario_2015" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -358,26 +358,31 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>

--- a/data/hydroExample/Power_HydroNetwork.xlsx
+++ b/data/hydroExample/Power_HydroNetwork.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E8CCB-0FC9-477C-9312-DEEEC962A5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC34309-6698-4315-9B29-3ADB973B8EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario_2015" sheetId="1" r:id="rId1"/>
+    <sheet name="Scenario_2016" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/hydroExample/Power_HydroNetwork.xlsx
+++ b/data/hydroExample/Power_HydroNetwork.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC34309-6698-4315-9B29-3ADB973B8EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1E1430-A350-46A8-8A5F-B11D371E7AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario_2016" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="72">
   <si>
     <t>Format:</t>
   </si>
@@ -339,7 +339,10 @@
     <t>244 Retznei</t>
   </si>
   <si>
-    <t>hydroExample</t>
+    <t>StylizedAustriaInEurope</t>
+  </si>
+  <si>
+    <t>HydroHintermuhr</t>
   </si>
 </sst>
 </file>
@@ -979,7 +982,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1001,7 +1004,7 @@
         <v>70</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1023,7 +1026,7 @@
         <v>70</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1045,7 +1048,7 @@
         <v>70</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1067,7 +1070,7 @@
         <v>70</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1089,7 +1092,7 @@
         <v>70</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,7 +1114,7 @@
         <v>70</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,7 +1136,7 @@
         <v>70</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1155,7 +1158,7 @@
         <v>70</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1177,7 +1180,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1199,7 +1202,7 @@
         <v>70</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1221,7 +1224,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1243,7 +1246,7 @@
         <v>70</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1265,7 +1268,7 @@
         <v>70</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1287,7 +1290,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1309,7 +1312,7 @@
         <v>70</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1331,7 +1334,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1353,7 +1356,7 @@
         <v>70</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,7 +1378,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,7 +1400,7 @@
         <v>70</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,7 +1422,7 @@
         <v>70</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1441,7 +1444,7 @@
         <v>70</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1463,7 +1466,7 @@
         <v>70</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1485,7 +1488,7 @@
         <v>70</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1507,7 +1510,7 @@
         <v>70</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1529,7 +1532,7 @@
         <v>70</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1551,7 +1554,7 @@
         <v>70</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1572,7 +1575,7 @@
         <v>70</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1593,7 +1596,7 @@
         <v>70</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1614,7 +1617,7 @@
         <v>70</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1635,7 +1638,7 @@
         <v>70</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1656,7 +1659,7 @@
         <v>70</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1680,7 @@
         <v>70</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -1698,7 +1701,7 @@
         <v>70</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1719,7 +1722,7 @@
         <v>70</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1740,7 +1743,7 @@
         <v>70</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
